--- a/Thread Chart/Perry Ellis Thread Charts.xlsx
+++ b/Thread Chart/Perry Ellis Thread Charts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\fs1\InformationManagement\Procedures &amp; References\Embroidery Thread Charts\Completed\Perry Ellis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B8B5ECE-A3F3-4665-939B-1C22F21622A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{46CB989D-76F3-4CF5-9418-9E305830DDE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22920" yWindow="-1095" windowWidth="29040" windowHeight="15840" xr2:uid="{68528003-038F-4264-AECD-F3165519D3C7}"/>
+    <workbookView xWindow="19090" yWindow="-5720" windowWidth="38620" windowHeight="21100" xr2:uid="{68528003-038F-4264-AECD-F3165519D3C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Madeira Polyneon" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Madeira Polyneon'!$A$1:$I$325</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -75,9 +75,6 @@
   </si>
   <si>
     <t>Madeira Polyneon</t>
-  </si>
-  <si>
-    <t>Black 3</t>
   </si>
   <si>
     <t>Black 4</t>
@@ -137,6 +134,9 @@
     <t>Black 7</t>
   </si>
   <si>
+    <t>Black 3</t>
+  </si>
+  <si>
     <t>Greens</t>
   </si>
   <si>
@@ -174,7 +174,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3044,8 +3044,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D44A3233-1477-4964-AC3F-567ED4F9E6FB}">
-  <dimension ref="A1:I325"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O325"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" style="2" customWidth="1"/>
@@ -3053,14 +3053,14 @@
     <col min="4" max="4" width="19.7109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.7109375" style="2" customWidth="1"/>
-    <col min="7" max="9" width="8.85546875" style="2"/>
-    <col min="10" max="10" width="20.7109375" style="2" customWidth="1"/>
-    <col min="11" max="14" width="8.85546875" style="2"/>
-    <col min="15" max="15" width="50.7109375" style="2" customWidth="1"/>
-    <col min="16" max="16384" width="8.85546875" style="2"/>
+    <col min="7" max="9" width="8.85546875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="11" max="14" width="8.85546875" style="2" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="50.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.85546875" style="2" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="50.1" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3089,7 +3089,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="50.1" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2" s="2">
         <v>48</v>
@@ -3116,7 +3116,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="50.1" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3" s="2">
         <v>16</v>
@@ -3143,12 +3143,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="50.1" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>11</v>
@@ -3170,12 +3170,12 @@
         <v>230</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="50.1" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>11</v>
@@ -3197,12 +3197,12 @@
         <v>234</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="50.1" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>11</v>
@@ -3224,12 +3224,12 @@
         <v>230</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="50.1" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>11</v>
@@ -3251,12 +3251,12 @@
         <v>233</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="50.1" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>11</v>
@@ -3278,12 +3278,12 @@
         <v>232</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="50.1" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>11</v>
@@ -3305,12 +3305,12 @@
         <v>214</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="50.1" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>11</v>
@@ -3332,12 +3332,12 @@
         <v>233</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="50.1" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>11</v>
@@ -3359,12 +3359,12 @@
         <v>233</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="50.1" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>11</v>
@@ -3386,12 +3386,12 @@
         <v>233</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="50.1" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>11</v>
@@ -3413,12 +3413,12 @@
         <v>233</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="50.1" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>11</v>
@@ -3440,12 +3440,12 @@
         <v>217</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="50.1" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>11</v>
@@ -3467,12 +3467,12 @@
         <v>232</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="50.1" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>11</v>
@@ -3494,12 +3494,12 @@
         <v>226</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="50.1" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>11</v>
@@ -3521,12 +3521,12 @@
         <v>226</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="50.1" customHeight="1">
       <c r="A18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>11</v>
@@ -3548,12 +3548,12 @@
         <v>195</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="50.1" customHeight="1">
       <c r="A19" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>11</v>
@@ -3575,12 +3575,12 @@
         <v>219</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="50.1" customHeight="1">
       <c r="A20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>11</v>
@@ -3602,12 +3602,12 @@
         <v>223</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="50.1" customHeight="1">
       <c r="A21" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>11</v>
@@ -3629,12 +3629,12 @@
         <v>222</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="50.1" customHeight="1">
       <c r="A22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>11</v>
@@ -3656,12 +3656,12 @@
         <v>191</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="50.1" customHeight="1">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>11</v>
@@ -3683,12 +3683,12 @@
         <v>166</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="50.1" customHeight="1">
       <c r="A24" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>11</v>
@@ -3710,12 +3710,12 @@
         <v>167</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="50.1" customHeight="1">
       <c r="A25" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>11</v>
@@ -3737,12 +3737,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="50.1" customHeight="1">
       <c r="A26" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>11</v>
@@ -3764,12 +3764,12 @@
         <v>173</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="50.1" customHeight="1">
       <c r="A27" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>11</v>
@@ -3791,12 +3791,12 @@
         <v>171</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="50.1" customHeight="1">
       <c r="A28" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>11</v>
@@ -3818,12 +3818,12 @@
         <v>184</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="50.1" customHeight="1">
       <c r="A29" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>11</v>
@@ -3845,12 +3845,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="50.1" customHeight="1">
       <c r="A30" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>11</v>
@@ -3872,12 +3872,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="50.1" customHeight="1">
       <c r="A31" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>11</v>
@@ -3899,12 +3899,12 @@
         <v>137</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="50.1" customHeight="1">
       <c r="A32" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>11</v>
@@ -3926,12 +3926,12 @@
         <v>138</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="50.1" customHeight="1">
       <c r="A33" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>11</v>
@@ -3953,12 +3953,12 @@
         <v>141</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="50.1" customHeight="1">
       <c r="A34" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>11</v>
@@ -3980,12 +3980,12 @@
         <v>112</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="50.1" customHeight="1">
       <c r="A35" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>11</v>
@@ -4007,12 +4007,12 @@
         <v>133</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" ht="50.1" customHeight="1">
       <c r="A36" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>11</v>
@@ -4034,12 +4034,12 @@
         <v>102</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" ht="50.1" customHeight="1">
       <c r="A37" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>11</v>
@@ -4061,12 +4061,12 @@
         <v>114</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" ht="50.1" customHeight="1">
       <c r="A38" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>11</v>
@@ -4088,12 +4088,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" ht="50.1" customHeight="1">
       <c r="A39" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>11</v>
@@ -4115,12 +4115,12 @@
         <v>105</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" ht="50.1" customHeight="1">
       <c r="A40" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>11</v>
@@ -4142,12 +4142,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" ht="50.1" customHeight="1">
       <c r="A41" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>11</v>
@@ -4169,12 +4169,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" ht="50.1" customHeight="1">
       <c r="A42" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>11</v>
@@ -4196,12 +4196,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" ht="50.1" customHeight="1">
       <c r="A43" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>11</v>
@@ -4223,12 +4223,12 @@
         <v>69</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" ht="50.1" customHeight="1">
       <c r="A44" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>11</v>
@@ -4250,12 +4250,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" ht="50.1" customHeight="1">
       <c r="A45" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>11</v>
@@ -4277,12 +4277,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" ht="50.1" customHeight="1">
       <c r="A46" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>11</v>
@@ -4304,12 +4304,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" ht="50.1" customHeight="1">
       <c r="A47" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>11</v>
@@ -4331,12 +4331,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" ht="50.1" customHeight="1">
       <c r="A48" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>11</v>
@@ -4358,12 +4358,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" ht="50.1" customHeight="1">
       <c r="A49" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>11</v>
@@ -4385,12 +4385,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" ht="50.1" customHeight="1">
       <c r="A50" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>11</v>
@@ -4412,12 +4412,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" ht="50.1" customHeight="1">
       <c r="A51" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>11</v>
@@ -4439,12 +4439,12 @@
         <v>215</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" ht="50.1" customHeight="1">
       <c r="A52" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>11</v>
@@ -4466,12 +4466,12 @@
         <v>179</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" ht="50.1" customHeight="1">
       <c r="A53" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>11</v>
@@ -4493,12 +4493,12 @@
         <v>136</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" ht="50.1" customHeight="1">
       <c r="A54" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>11</v>
@@ -4520,12 +4520,12 @@
         <v>165</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" ht="50.1" customHeight="1">
       <c r="A55" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>11</v>
@@ -4547,12 +4547,12 @@
         <v>93</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" ht="50.1" customHeight="1">
       <c r="A56" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>11</v>
@@ -4574,12 +4574,12 @@
         <v>138</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" ht="50.1" customHeight="1">
       <c r="A57" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>11</v>
@@ -4601,12 +4601,12 @@
         <v>133</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" ht="50.1" customHeight="1">
       <c r="A58" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>11</v>
@@ -4628,12 +4628,12 @@
         <v>172</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" ht="50.1" customHeight="1">
       <c r="A59" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>11</v>
@@ -4655,12 +4655,12 @@
         <v>132</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" ht="50.1" customHeight="1">
       <c r="A60" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>11</v>
@@ -4682,12 +4682,12 @@
         <v>132</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" ht="50.1" customHeight="1">
       <c r="A61" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>11</v>
@@ -4709,12 +4709,12 @@
         <v>145</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" ht="50.1" customHeight="1">
       <c r="A62" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>11</v>
@@ -4736,12 +4736,12 @@
         <v>145</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" ht="50.1" customHeight="1">
       <c r="A63" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>11</v>
@@ -4763,12 +4763,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" ht="50.1" customHeight="1">
       <c r="A64" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>11</v>
@@ -4790,12 +4790,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" ht="50.1" customHeight="1">
       <c r="A65" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>11</v>
@@ -4817,12 +4817,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" ht="50.1" customHeight="1">
       <c r="A66" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>11</v>
@@ -4844,12 +4844,12 @@
         <v>101</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" ht="50.1" customHeight="1">
       <c r="A67" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>11</v>
@@ -4871,12 +4871,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" ht="50.1" customHeight="1">
       <c r="A68" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>11</v>
@@ -4898,12 +4898,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" ht="50.1" customHeight="1">
       <c r="A69" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>11</v>
@@ -4925,12 +4925,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" ht="50.1" customHeight="1">
       <c r="A70" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>11</v>
@@ -4952,12 +4952,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" ht="50.1" customHeight="1">
       <c r="A71" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>11</v>
@@ -4979,12 +4979,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" ht="50.1" customHeight="1">
       <c r="A72" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>11</v>
@@ -5006,12 +5006,12 @@
         <v>130</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" ht="50.1" customHeight="1">
       <c r="A73" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>11</v>
@@ -5033,12 +5033,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" ht="50.1" customHeight="1">
       <c r="A74" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>11</v>
@@ -5060,12 +5060,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" ht="50.1" customHeight="1">
       <c r="A75" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>11</v>
@@ -5087,12 +5087,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" ht="50.1" customHeight="1">
       <c r="A76" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>11</v>
@@ -5114,12 +5114,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" ht="50.1" customHeight="1">
       <c r="A77" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>11</v>
@@ -5141,12 +5141,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" ht="50.1" customHeight="1">
       <c r="A78" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>11</v>
@@ -5168,12 +5168,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" ht="50.1" customHeight="1">
       <c r="A79" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>11</v>
@@ -5195,12 +5195,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" ht="50.1" customHeight="1">
       <c r="A80" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>11</v>
@@ -5222,12 +5222,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" ht="50.1" customHeight="1">
       <c r="A81" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>11</v>
@@ -5249,12 +5249,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" ht="50.1" customHeight="1">
       <c r="A82" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>11</v>
@@ -5276,12 +5276,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" ht="50.1" customHeight="1">
       <c r="A83" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>11</v>
@@ -5303,12 +5303,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" ht="50.1" customHeight="1">
       <c r="A84" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>11</v>
@@ -5330,12 +5330,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" ht="50.1" customHeight="1">
       <c r="A85" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>11</v>
@@ -5357,12 +5357,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" ht="50.1" customHeight="1">
       <c r="A86" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>11</v>
@@ -5384,12 +5384,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" ht="50.1" customHeight="1">
       <c r="A87" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>11</v>
@@ -5411,12 +5411,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" ht="50.1" customHeight="1">
       <c r="A88" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>11</v>
@@ -5438,12 +5438,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" ht="50.1" customHeight="1">
       <c r="A89" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>11</v>
@@ -5465,12 +5465,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" ht="50.1" customHeight="1">
       <c r="A90" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>11</v>
@@ -5492,12 +5492,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" ht="50.1" customHeight="1">
       <c r="A91" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>11</v>
@@ -5519,12 +5519,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" ht="50.1" customHeight="1">
       <c r="A92" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>11</v>
@@ -5546,12 +5546,12 @@
         <v>229</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" ht="50.1" customHeight="1">
       <c r="A93" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>11</v>
@@ -5573,12 +5573,12 @@
         <v>210</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" ht="50.1" customHeight="1">
       <c r="A94" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>11</v>
@@ -5600,12 +5600,12 @@
         <v>232</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" ht="50.1" customHeight="1">
       <c r="A95" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>11</v>
@@ -5627,12 +5627,12 @@
         <v>198</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" ht="50.1" customHeight="1">
       <c r="A96" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>11</v>
@@ -5654,12 +5654,12 @@
         <v>217</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" ht="50.1" customHeight="1">
       <c r="A97" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>11</v>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="E97" s="89"/>
       <c r="F97" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G97" s="2">
         <v>201</v>
@@ -5681,12 +5681,12 @@
         <v>201</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" ht="50.1" customHeight="1">
       <c r="A98" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>11</v>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="E98" s="90"/>
       <c r="F98" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G98" s="2">
         <v>188</v>
@@ -5708,12 +5708,12 @@
         <v>188</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" ht="50.1" customHeight="1">
       <c r="A99" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>11</v>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="E99" s="91"/>
       <c r="F99" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G99" s="2">
         <v>178</v>
@@ -5735,12 +5735,12 @@
         <v>178</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" ht="50.1" customHeight="1">
       <c r="A100" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>11</v>
@@ -5762,12 +5762,12 @@
         <v>172</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" ht="50.1" customHeight="1">
       <c r="A101" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>11</v>
@@ -5789,12 +5789,12 @@
         <v>159</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" ht="50.1" customHeight="1">
       <c r="A102" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>11</v>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="E102" s="94"/>
       <c r="F102" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G102" s="2">
         <v>169</v>
@@ -5816,12 +5816,12 @@
         <v>168</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" ht="50.1" customHeight="1">
       <c r="A103" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>11</v>
@@ -5843,12 +5843,12 @@
         <v>159</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" ht="50.1" customHeight="1">
       <c r="A104" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>11</v>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="E104" s="96"/>
       <c r="F104" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G104" s="2">
         <v>167</v>
@@ -5870,12 +5870,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" ht="50.1" customHeight="1">
       <c r="A105" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>11</v>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="E105" s="97"/>
       <c r="F105" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G105" s="2">
         <v>153</v>
@@ -5897,12 +5897,12 @@
         <v>152</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" ht="50.1" customHeight="1">
       <c r="A106" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>11</v>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="E106" s="97"/>
       <c r="F106" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G106" s="2">
         <v>153</v>
@@ -5924,12 +5924,12 @@
         <v>152</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" ht="50.1" customHeight="1">
       <c r="A107" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>11</v>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="E107" s="98"/>
       <c r="F107" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G107" s="2">
         <v>150</v>
@@ -5951,12 +5951,12 @@
         <v>130</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" ht="50.1" customHeight="1">
       <c r="A108" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>11</v>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="E108" s="99"/>
       <c r="F108" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G108" s="2">
         <v>137</v>
@@ -5978,12 +5978,12 @@
         <v>140</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" ht="50.1" customHeight="1">
       <c r="A109" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>11</v>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="E109" s="99"/>
       <c r="F109" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G109" s="2">
         <v>137</v>
@@ -6005,12 +6005,12 @@
         <v>140</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" ht="50.1" customHeight="1">
       <c r="A110" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>11</v>
@@ -6032,12 +6032,12 @@
         <v>139</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" ht="50.1" customHeight="1">
       <c r="A111" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>11</v>
@@ -6059,12 +6059,12 @@
         <v>139</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" ht="50.1" customHeight="1">
       <c r="A112" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>11</v>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="E112" s="101"/>
       <c r="F112" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G112" s="2">
         <v>141</v>
@@ -6086,12 +6086,12 @@
         <v>121</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" ht="50.1" customHeight="1">
       <c r="A113" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>11</v>
@@ -6113,12 +6113,12 @@
         <v>139</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" ht="50.1" customHeight="1">
       <c r="A114" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>11</v>
@@ -6128,7 +6128,7 @@
       </c>
       <c r="E114" s="103"/>
       <c r="F114" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G114" s="2">
         <v>132</v>
@@ -6140,12 +6140,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" ht="50.1" customHeight="1">
       <c r="A115" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>11</v>
@@ -6155,7 +6155,7 @@
       </c>
       <c r="E115" s="104"/>
       <c r="F115" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G115" s="2">
         <v>118</v>
@@ -6167,12 +6167,12 @@
         <v>120</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" ht="50.1" customHeight="1">
       <c r="A116" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>11</v>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="E116" s="104"/>
       <c r="F116" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G116" s="2">
         <v>118</v>
@@ -6194,12 +6194,12 @@
         <v>120</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" ht="50.1" customHeight="1">
       <c r="A117" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>11</v>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="E117" s="105"/>
       <c r="F117" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G117" s="2">
         <v>122</v>
@@ -6221,12 +6221,12 @@
         <v>101</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" ht="50.1" customHeight="1">
       <c r="A118" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>11</v>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="E118" s="105"/>
       <c r="F118" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G118" s="2">
         <v>122</v>
@@ -6248,12 +6248,12 @@
         <v>101</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" ht="50.1" customHeight="1">
       <c r="A119" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>11</v>
@@ -6275,12 +6275,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" ht="50.1" customHeight="1">
       <c r="A120" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>11</v>
@@ -6302,12 +6302,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" ht="50.1" customHeight="1">
       <c r="A121" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>11</v>
@@ -6329,12 +6329,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" ht="50.1" customHeight="1">
       <c r="A122" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>11</v>
@@ -6356,12 +6356,12 @@
         <v>88</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" ht="50.1" customHeight="1">
       <c r="A123" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>11</v>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="E123" s="110"/>
       <c r="F123" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G123" s="2">
         <v>84</v>
@@ -6383,12 +6383,12 @@
         <v>88</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" ht="50.1" customHeight="1">
       <c r="A124" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>11</v>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="E124" s="110"/>
       <c r="F124" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G124" s="2">
         <v>84</v>
@@ -6410,12 +6410,12 @@
         <v>88</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" ht="50.1" customHeight="1">
       <c r="A125" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>11</v>
@@ -6437,12 +6437,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" ht="50.1" customHeight="1">
       <c r="A126" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>11</v>
@@ -6464,12 +6464,12 @@
         <v>69</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" ht="50.1" customHeight="1">
       <c r="A127" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>11</v>
@@ -6491,12 +6491,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" ht="50.1" customHeight="1">
       <c r="A128" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>11</v>
@@ -6518,12 +6518,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" ht="50.1" customHeight="1">
       <c r="A129" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>11</v>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="E129" s="114"/>
       <c r="F129" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G129" s="2">
         <v>60</v>
@@ -6545,12 +6545,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" ht="50.1" customHeight="1">
       <c r="A130" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>11</v>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="E130" s="114"/>
       <c r="F130" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G130" s="2">
         <v>60</v>
@@ -6572,12 +6572,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" ht="50.1" customHeight="1">
       <c r="A131" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>11</v>
@@ -6599,12 +6599,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" ht="50.1" customHeight="1">
       <c r="A132" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>11</v>
@@ -6626,12 +6626,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" ht="50.1" customHeight="1">
       <c r="A133" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>11</v>
@@ -6653,12 +6653,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" ht="50.1" customHeight="1">
       <c r="A134" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>11</v>
@@ -6680,12 +6680,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" ht="50.1" customHeight="1">
       <c r="A135" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>11</v>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="E135" s="3"/>
       <c r="F135" s="2" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="G135" s="2">
         <v>34</v>
@@ -6707,7 +6707,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" ht="50.1" customHeight="1">
       <c r="A136" s="2" t="s">
         <v>9</v>
       </c>
@@ -6734,7 +6734,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" ht="50.1" customHeight="1">
       <c r="A137" s="2" t="s">
         <v>9</v>
       </c>
@@ -6761,7 +6761,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" ht="50.1" customHeight="1">
       <c r="A138" s="2" t="s">
         <v>9</v>
       </c>
@@ -6788,7 +6788,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" ht="50.1" customHeight="1">
       <c r="A139" s="2" t="s">
         <v>9</v>
       </c>
@@ -6815,7 +6815,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" ht="50.1" customHeight="1">
       <c r="A140" s="2" t="s">
         <v>9</v>
       </c>
@@ -6842,7 +6842,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" ht="50.1" customHeight="1">
       <c r="A141" s="2" t="s">
         <v>9</v>
       </c>
@@ -6869,7 +6869,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" ht="50.1" customHeight="1">
       <c r="A142" s="2" t="s">
         <v>9</v>
       </c>
@@ -6896,7 +6896,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" ht="50.1" customHeight="1">
       <c r="A143" s="2" t="s">
         <v>9</v>
       </c>
@@ -6923,7 +6923,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" ht="50.1" customHeight="1">
       <c r="A144" s="2" t="s">
         <v>9</v>
       </c>
@@ -6950,7 +6950,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" ht="50.1" customHeight="1">
       <c r="A145" s="2" t="s">
         <v>9</v>
       </c>
@@ -6977,7 +6977,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" ht="50.1" customHeight="1">
       <c r="A146" s="2" t="s">
         <v>9</v>
       </c>
@@ -7004,7 +7004,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" ht="50.1" customHeight="1">
       <c r="A147" s="2" t="s">
         <v>9</v>
       </c>
@@ -7031,7 +7031,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" ht="50.1" customHeight="1">
       <c r="A148" s="2" t="s">
         <v>9</v>
       </c>
@@ -7058,7 +7058,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" ht="50.1" customHeight="1">
       <c r="A149" s="2" t="s">
         <v>9</v>
       </c>
@@ -7085,7 +7085,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" ht="50.1" customHeight="1">
       <c r="A150" s="2" t="s">
         <v>9</v>
       </c>
@@ -7112,7 +7112,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" ht="50.1" customHeight="1">
       <c r="A151" s="2" t="s">
         <v>9</v>
       </c>
@@ -7139,7 +7139,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" ht="50.1" customHeight="1">
       <c r="A152" s="2" t="s">
         <v>9</v>
       </c>
@@ -7166,7 +7166,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" ht="50.1" customHeight="1">
       <c r="A153" s="2" t="s">
         <v>9</v>
       </c>
@@ -7193,7 +7193,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" ht="50.1" customHeight="1">
       <c r="A154" s="2" t="s">
         <v>9</v>
       </c>
@@ -7220,7 +7220,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" ht="50.1" customHeight="1">
       <c r="A155" s="2" t="s">
         <v>9</v>
       </c>
@@ -7247,7 +7247,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" ht="50.1" customHeight="1">
       <c r="A156" s="2" t="s">
         <v>9</v>
       </c>
@@ -7274,7 +7274,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" ht="50.1" customHeight="1">
       <c r="A157" s="2" t="s">
         <v>9</v>
       </c>
@@ -7301,7 +7301,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" ht="50.1" customHeight="1">
       <c r="A158" s="2" t="s">
         <v>9</v>
       </c>
@@ -7328,7 +7328,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" ht="50.1" customHeight="1">
       <c r="A159" s="2" t="s">
         <v>9</v>
       </c>
@@ -7355,7 +7355,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" ht="50.1" customHeight="1">
       <c r="A160" s="2" t="s">
         <v>9</v>
       </c>
@@ -7382,7 +7382,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" ht="50.1" customHeight="1">
       <c r="A161" s="2" t="s">
         <v>9</v>
       </c>
@@ -7409,7 +7409,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" ht="50.1" customHeight="1">
       <c r="A162" s="2" t="s">
         <v>9</v>
       </c>
@@ -7436,7 +7436,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" ht="50.1" customHeight="1">
       <c r="A163" s="2" t="s">
         <v>9</v>
       </c>
@@ -7463,7 +7463,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" ht="50.1" customHeight="1">
       <c r="A164" s="2" t="s">
         <v>9</v>
       </c>
@@ -7490,7 +7490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" ht="50.1" customHeight="1">
       <c r="A165" s="2" t="s">
         <v>9</v>
       </c>
@@ -7517,7 +7517,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" ht="50.1" customHeight="1">
       <c r="A166" s="2" t="s">
         <v>9</v>
       </c>
@@ -7544,7 +7544,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" ht="50.1" customHeight="1">
       <c r="A167" s="2" t="s">
         <v>9</v>
       </c>
@@ -7571,7 +7571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" ht="50.1" customHeight="1">
       <c r="A168" s="2" t="s">
         <v>9</v>
       </c>
@@ -7598,7 +7598,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" ht="50.1" customHeight="1">
       <c r="A169" s="2" t="s">
         <v>9</v>
       </c>
@@ -7625,7 +7625,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" ht="50.1" customHeight="1">
       <c r="A170" s="2" t="s">
         <v>9</v>
       </c>
@@ -7652,7 +7652,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" ht="50.1" customHeight="1">
       <c r="A171" s="2" t="s">
         <v>9</v>
       </c>
@@ -7679,7 +7679,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" ht="50.1" customHeight="1">
       <c r="A172" s="2" t="s">
         <v>9</v>
       </c>
@@ -7706,7 +7706,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" ht="50.1" customHeight="1">
       <c r="A173" s="2" t="s">
         <v>9</v>
       </c>
@@ -7733,7 +7733,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" ht="50.1" customHeight="1">
       <c r="A174" s="2" t="s">
         <v>9</v>
       </c>
@@ -7760,7 +7760,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" ht="50.1" customHeight="1">
       <c r="A175" s="2" t="s">
         <v>9</v>
       </c>
@@ -7787,7 +7787,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" ht="50.1" customHeight="1">
       <c r="A176" s="2" t="s">
         <v>9</v>
       </c>
@@ -7814,7 +7814,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" ht="50.1" customHeight="1">
       <c r="A177" s="2" t="s">
         <v>9</v>
       </c>
@@ -7841,7 +7841,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" ht="50.1" customHeight="1">
       <c r="A178" s="2" t="s">
         <v>9</v>
       </c>
@@ -7868,7 +7868,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" ht="50.1" customHeight="1">
       <c r="A179" s="2" t="s">
         <v>9</v>
       </c>
@@ -7895,7 +7895,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" ht="50.1" customHeight="1">
       <c r="A180" s="2" t="s">
         <v>9</v>
       </c>
@@ -7922,7 +7922,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" ht="50.1" customHeight="1">
       <c r="A181" s="2" t="s">
         <v>9</v>
       </c>
@@ -7949,7 +7949,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" ht="50.1" customHeight="1">
       <c r="A182" s="2" t="s">
         <v>9</v>
       </c>
@@ -7976,7 +7976,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" ht="50.1" customHeight="1">
       <c r="A183" s="2" t="s">
         <v>9</v>
       </c>
@@ -8003,7 +8003,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" ht="50.1" customHeight="1">
       <c r="A184" s="2" t="s">
         <v>9</v>
       </c>
@@ -8030,7 +8030,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" ht="50.1" customHeight="1">
       <c r="A185" s="2" t="s">
         <v>9</v>
       </c>
@@ -8057,7 +8057,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="186" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" ht="50.1" customHeight="1">
       <c r="A186" s="2" t="s">
         <v>9</v>
       </c>
@@ -8084,7 +8084,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" ht="50.1" customHeight="1">
       <c r="A187" s="2" t="s">
         <v>9</v>
       </c>
@@ -8111,7 +8111,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" ht="50.1" customHeight="1">
       <c r="A188" s="2" t="s">
         <v>9</v>
       </c>
@@ -8138,7 +8138,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" ht="50.1" customHeight="1">
       <c r="A189" s="2" t="s">
         <v>9</v>
       </c>
@@ -8165,7 +8165,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" ht="50.1" customHeight="1">
       <c r="A190" s="2" t="s">
         <v>9</v>
       </c>
@@ -8192,7 +8192,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" ht="50.1" customHeight="1">
       <c r="A191" s="2" t="s">
         <v>9</v>
       </c>
@@ -8219,7 +8219,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" ht="50.1" customHeight="1">
       <c r="A192" s="2" t="s">
         <v>9</v>
       </c>
@@ -8246,7 +8246,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" ht="50.1" customHeight="1">
       <c r="A193" s="2" t="s">
         <v>9</v>
       </c>
@@ -8273,7 +8273,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" ht="50.1" customHeight="1">
       <c r="A194" s="2" t="s">
         <v>9</v>
       </c>
@@ -8300,7 +8300,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" ht="50.1" customHeight="1">
       <c r="A195" s="2" t="s">
         <v>9</v>
       </c>
@@ -8327,7 +8327,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" ht="50.1" customHeight="1">
       <c r="A196" s="2" t="s">
         <v>9</v>
       </c>
@@ -8354,7 +8354,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" ht="50.1" customHeight="1">
       <c r="A197" s="2" t="s">
         <v>9</v>
       </c>
@@ -8381,7 +8381,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" ht="50.1" customHeight="1">
       <c r="A198" s="2" t="s">
         <v>9</v>
       </c>
@@ -8408,7 +8408,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" ht="50.1" customHeight="1">
       <c r="A199" s="2" t="s">
         <v>9</v>
       </c>
@@ -8435,7 +8435,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" ht="50.1" customHeight="1">
       <c r="A200" s="2" t="s">
         <v>9</v>
       </c>
@@ -8462,7 +8462,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" ht="50.1" customHeight="1">
       <c r="A201" s="2" t="s">
         <v>9</v>
       </c>
@@ -8489,7 +8489,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" ht="50.1" customHeight="1">
       <c r="A202" s="2" t="s">
         <v>9</v>
       </c>
@@ -8516,7 +8516,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" ht="50.1" customHeight="1">
       <c r="A203" s="2" t="s">
         <v>9</v>
       </c>
@@ -8543,7 +8543,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" ht="50.1" customHeight="1">
       <c r="A204" s="2" t="s">
         <v>9</v>
       </c>
@@ -8570,7 +8570,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" ht="50.1" customHeight="1">
       <c r="A205" s="2" t="s">
         <v>9</v>
       </c>
@@ -8597,7 +8597,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" ht="50.1" customHeight="1">
       <c r="A206" s="2" t="s">
         <v>9</v>
       </c>
@@ -8624,7 +8624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" ht="50.1" customHeight="1">
       <c r="A207" s="2" t="s">
         <v>9</v>
       </c>
@@ -8651,7 +8651,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" ht="50.1" customHeight="1">
       <c r="A208" s="2" t="s">
         <v>9</v>
       </c>
@@ -8678,7 +8678,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" ht="50.1" customHeight="1">
       <c r="A209" s="2" t="s">
         <v>9</v>
       </c>
@@ -8705,7 +8705,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" ht="50.1" customHeight="1">
       <c r="A210" s="2" t="s">
         <v>9</v>
       </c>
@@ -8732,7 +8732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" ht="50.1" customHeight="1">
       <c r="A211" s="2" t="s">
         <v>9</v>
       </c>
@@ -8759,7 +8759,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" ht="50.1" customHeight="1">
       <c r="A212" s="2" t="s">
         <v>9</v>
       </c>
@@ -8786,7 +8786,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" ht="50.1" customHeight="1">
       <c r="A213" s="2" t="s">
         <v>9</v>
       </c>
@@ -8813,7 +8813,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" ht="50.1" customHeight="1">
       <c r="A214" s="2" t="s">
         <v>9</v>
       </c>
@@ -8840,7 +8840,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" ht="50.1" customHeight="1">
       <c r="A215" s="2" t="s">
         <v>9</v>
       </c>
@@ -8867,7 +8867,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" ht="50.1" customHeight="1">
       <c r="A216" s="2" t="s">
         <v>9</v>
       </c>
@@ -8894,7 +8894,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" ht="50.1" customHeight="1">
       <c r="A217" s="2" t="s">
         <v>9</v>
       </c>
@@ -8921,7 +8921,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" ht="50.1" customHeight="1">
       <c r="A218" s="2" t="s">
         <v>9</v>
       </c>
@@ -8948,7 +8948,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" ht="50.1" customHeight="1">
       <c r="A219" s="2" t="s">
         <v>9</v>
       </c>
@@ -8975,7 +8975,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" ht="50.1" customHeight="1">
       <c r="A220" s="2" t="s">
         <v>9</v>
       </c>
@@ -9002,7 +9002,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" ht="50.1" customHeight="1">
       <c r="A221" s="2" t="s">
         <v>9</v>
       </c>
@@ -9029,7 +9029,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" ht="50.1" customHeight="1">
       <c r="A222" s="2" t="s">
         <v>9</v>
       </c>
@@ -9056,7 +9056,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" ht="50.1" customHeight="1">
       <c r="A223" s="2" t="s">
         <v>9</v>
       </c>
@@ -9083,7 +9083,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" ht="50.1" customHeight="1">
       <c r="A224" s="2" t="s">
         <v>9</v>
       </c>
@@ -9110,7 +9110,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" ht="50.1" customHeight="1">
       <c r="A225" s="2" t="s">
         <v>9</v>
       </c>
@@ -9137,7 +9137,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="226" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" ht="50.1" customHeight="1">
       <c r="A226" s="2" t="s">
         <v>9</v>
       </c>
@@ -9164,7 +9164,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" ht="50.1" customHeight="1">
       <c r="A227" s="2" t="s">
         <v>9</v>
       </c>
@@ -9191,7 +9191,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" ht="50.1" customHeight="1">
       <c r="A228" s="2" t="s">
         <v>9</v>
       </c>
@@ -9218,7 +9218,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" ht="50.1" customHeight="1">
       <c r="A229" s="2" t="s">
         <v>9</v>
       </c>
@@ -9245,7 +9245,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" ht="50.1" customHeight="1">
       <c r="A230" s="2" t="s">
         <v>9</v>
       </c>
@@ -9272,7 +9272,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" ht="50.1" customHeight="1">
       <c r="A231" s="2" t="s">
         <v>9</v>
       </c>
@@ -9299,7 +9299,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" ht="50.1" customHeight="1">
       <c r="A232" s="2" t="s">
         <v>9</v>
       </c>
@@ -9326,7 +9326,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" ht="50.1" customHeight="1">
       <c r="A233" s="2" t="s">
         <v>9</v>
       </c>
@@ -9353,7 +9353,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" ht="50.1" customHeight="1">
       <c r="A234" s="2" t="s">
         <v>9</v>
       </c>
@@ -9380,7 +9380,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="235" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" ht="50.1" customHeight="1">
       <c r="A235" s="2" t="s">
         <v>9</v>
       </c>
@@ -9407,7 +9407,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="236" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" ht="50.1" customHeight="1">
       <c r="A236" s="2" t="s">
         <v>9</v>
       </c>
@@ -9434,7 +9434,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" ht="50.1" customHeight="1">
       <c r="A237" s="2" t="s">
         <v>9</v>
       </c>
@@ -9461,7 +9461,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" ht="50.1" customHeight="1">
       <c r="A238" s="2" t="s">
         <v>9</v>
       </c>
@@ -9488,7 +9488,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="239" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" ht="50.1" customHeight="1">
       <c r="A239" s="2" t="s">
         <v>9</v>
       </c>
@@ -9515,7 +9515,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="240" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" ht="50.1" customHeight="1">
       <c r="A240" s="2" t="s">
         <v>9</v>
       </c>
@@ -9542,7 +9542,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="241" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" ht="50.1" customHeight="1">
       <c r="A241" s="2" t="s">
         <v>9</v>
       </c>
@@ -9569,7 +9569,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="242" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" ht="50.1" customHeight="1">
       <c r="A242" s="2" t="s">
         <v>9</v>
       </c>
@@ -9596,7 +9596,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="243" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" ht="50.1" customHeight="1">
       <c r="A243" s="2" t="s">
         <v>9</v>
       </c>
@@ -9623,7 +9623,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="244" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" ht="50.1" customHeight="1">
       <c r="A244" s="2" t="s">
         <v>9</v>
       </c>
@@ -9650,7 +9650,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" ht="50.1" customHeight="1">
       <c r="A245" s="2" t="s">
         <v>9</v>
       </c>
@@ -9677,7 +9677,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="246" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" ht="50.1" customHeight="1">
       <c r="A246" s="2" t="s">
         <v>9</v>
       </c>
@@ -9704,7 +9704,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="247" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" ht="50.1" customHeight="1">
       <c r="A247" s="2" t="s">
         <v>9</v>
       </c>
@@ -9731,7 +9731,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" ht="50.1" customHeight="1">
       <c r="A248" s="2" t="s">
         <v>9</v>
       </c>
@@ -9758,7 +9758,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" ht="50.1" customHeight="1">
       <c r="A249" s="2" t="s">
         <v>9</v>
       </c>
@@ -9785,7 +9785,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="250" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" ht="50.1" customHeight="1">
       <c r="A250" s="2" t="s">
         <v>9</v>
       </c>
@@ -9812,7 +9812,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" ht="50.1" customHeight="1">
       <c r="A251" s="2" t="s">
         <v>9</v>
       </c>
@@ -9839,7 +9839,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" ht="50.1" customHeight="1">
       <c r="A252" s="2" t="s">
         <v>9</v>
       </c>
@@ -9866,7 +9866,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="253" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" ht="50.1" customHeight="1">
       <c r="A253" s="2" t="s">
         <v>9</v>
       </c>
@@ -9893,7 +9893,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" ht="50.1" customHeight="1">
       <c r="A254" s="2" t="s">
         <v>9</v>
       </c>
@@ -9920,7 +9920,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="255" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" ht="50.1" customHeight="1">
       <c r="A255" s="2" t="s">
         <v>9</v>
       </c>
@@ -9947,7 +9947,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="256" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" ht="50.1" customHeight="1">
       <c r="A256" s="2" t="s">
         <v>9</v>
       </c>
@@ -9974,7 +9974,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="257" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" ht="50.1" customHeight="1">
       <c r="A257" s="2" t="s">
         <v>9</v>
       </c>
@@ -10001,7 +10001,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" ht="50.1" customHeight="1">
       <c r="A258" s="2" t="s">
         <v>9</v>
       </c>
@@ -10028,7 +10028,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="259" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" ht="50.1" customHeight="1">
       <c r="A259" s="2" t="s">
         <v>9</v>
       </c>
@@ -10055,7 +10055,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="260" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" ht="50.1" customHeight="1">
       <c r="A260" s="2" t="s">
         <v>9</v>
       </c>
@@ -10082,7 +10082,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="261" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" ht="50.1" customHeight="1">
       <c r="A261" s="2" t="s">
         <v>9</v>
       </c>
@@ -10109,7 +10109,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="262" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" ht="50.1" customHeight="1">
       <c r="A262" s="2" t="s">
         <v>9</v>
       </c>
@@ -10136,7 +10136,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="263" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" ht="50.1" customHeight="1">
       <c r="A263" s="2" t="s">
         <v>9</v>
       </c>
@@ -10163,7 +10163,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="264" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" ht="50.1" customHeight="1">
       <c r="A264" s="2" t="s">
         <v>9</v>
       </c>
@@ -10190,7 +10190,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="265" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" ht="50.1" customHeight="1">
       <c r="A265" s="2" t="s">
         <v>9</v>
       </c>
@@ -10217,7 +10217,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="266" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" ht="50.1" customHeight="1">
       <c r="A266" s="2" t="s">
         <v>9</v>
       </c>
@@ -10244,7 +10244,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="267" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" ht="50.1" customHeight="1">
       <c r="A267" s="2" t="s">
         <v>9</v>
       </c>
@@ -10271,7 +10271,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="268" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" ht="50.1" customHeight="1">
       <c r="A268" s="2" t="s">
         <v>9</v>
       </c>
@@ -10298,7 +10298,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="269" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" ht="50.1" customHeight="1">
       <c r="A269" s="2" t="s">
         <v>9</v>
       </c>
@@ -10325,7 +10325,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="270" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" ht="50.1" customHeight="1">
       <c r="A270" s="2" t="s">
         <v>9</v>
       </c>
@@ -10352,7 +10352,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="271" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" ht="50.1" customHeight="1">
       <c r="A271" s="2" t="s">
         <v>9</v>
       </c>
@@ -10379,7 +10379,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="272" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" ht="50.1" customHeight="1">
       <c r="A272" s="2" t="s">
         <v>9</v>
       </c>
@@ -10406,7 +10406,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="273" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" ht="50.1" customHeight="1">
       <c r="A273" s="2" t="s">
         <v>9</v>
       </c>
@@ -10433,7 +10433,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="274" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" ht="50.1" customHeight="1">
       <c r="A274" s="2" t="s">
         <v>9</v>
       </c>
@@ -10460,7 +10460,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="275" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" ht="50.1" customHeight="1">
       <c r="A275" s="2" t="s">
         <v>9</v>
       </c>
@@ -10487,7 +10487,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="276" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" ht="50.1" customHeight="1">
       <c r="A276" s="2" t="s">
         <v>9</v>
       </c>
@@ -10514,7 +10514,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="277" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" ht="50.1" customHeight="1">
       <c r="A277" s="2" t="s">
         <v>9</v>
       </c>
@@ -10541,7 +10541,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="278" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" ht="50.1" customHeight="1">
       <c r="A278" s="2" t="s">
         <v>9</v>
       </c>
@@ -10568,7 +10568,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="279" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" ht="50.1" customHeight="1">
       <c r="A279" s="2" t="s">
         <v>9</v>
       </c>
@@ -10595,7 +10595,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="280" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" ht="50.1" customHeight="1">
       <c r="A280" s="2" t="s">
         <v>9</v>
       </c>
@@ -10622,7 +10622,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="281" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" ht="50.1" customHeight="1">
       <c r="A281" s="2" t="s">
         <v>9</v>
       </c>
@@ -10649,7 +10649,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="282" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" ht="50.1" customHeight="1">
       <c r="A282" s="2" t="s">
         <v>9</v>
       </c>
@@ -10676,7 +10676,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="283" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" ht="50.1" customHeight="1">
       <c r="A283" s="2" t="s">
         <v>9</v>
       </c>
@@ -10703,7 +10703,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="284" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" ht="50.1" customHeight="1">
       <c r="A284" s="2" t="s">
         <v>9</v>
       </c>
@@ -10730,7 +10730,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="285" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" ht="50.1" customHeight="1">
       <c r="A285" s="2" t="s">
         <v>9</v>
       </c>
@@ -10757,7 +10757,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="286" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" ht="50.1" customHeight="1">
       <c r="A286" s="2" t="s">
         <v>9</v>
       </c>
@@ -10784,7 +10784,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="287" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" ht="50.1" customHeight="1">
       <c r="A287" s="2" t="s">
         <v>9</v>
       </c>
@@ -10811,7 +10811,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="288" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" ht="50.1" customHeight="1">
       <c r="A288" s="2" t="s">
         <v>9</v>
       </c>
@@ -10838,7 +10838,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="289" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" ht="50.1" customHeight="1">
       <c r="A289" s="2" t="s">
         <v>9</v>
       </c>
@@ -10865,7 +10865,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="290" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" ht="50.1" customHeight="1">
       <c r="A290" s="2" t="s">
         <v>9</v>
       </c>
@@ -10892,7 +10892,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="291" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" ht="50.1" customHeight="1">
       <c r="A291" s="2" t="s">
         <v>9</v>
       </c>
@@ -10919,7 +10919,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="292" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" ht="50.1" customHeight="1">
       <c r="A292" s="2" t="s">
         <v>9</v>
       </c>
@@ -10946,7 +10946,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="293" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" ht="50.1" customHeight="1">
       <c r="A293" s="2" t="s">
         <v>9</v>
       </c>
@@ -10973,7 +10973,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="294" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" ht="50.1" customHeight="1">
       <c r="A294" s="2" t="s">
         <v>9</v>
       </c>
@@ -11000,7 +11000,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="295" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" ht="50.1" customHeight="1">
       <c r="A295" s="2" t="s">
         <v>9</v>
       </c>
@@ -11027,7 +11027,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="296" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" ht="50.1" customHeight="1">
       <c r="A296" s="2" t="s">
         <v>9</v>
       </c>
@@ -11054,7 +11054,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="297" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" ht="50.1" customHeight="1">
       <c r="A297" s="2" t="s">
         <v>9</v>
       </c>
@@ -11081,7 +11081,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="298" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" ht="50.1" customHeight="1">
       <c r="A298" s="2" t="s">
         <v>9</v>
       </c>
@@ -11108,7 +11108,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="299" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" ht="50.1" customHeight="1">
       <c r="A299" s="2" t="s">
         <v>9</v>
       </c>
@@ -11135,7 +11135,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="300" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" ht="50.1" customHeight="1">
       <c r="A300" s="2" t="s">
         <v>9</v>
       </c>
@@ -11162,7 +11162,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="301" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" ht="50.1" customHeight="1">
       <c r="A301" s="2" t="s">
         <v>9</v>
       </c>
@@ -11189,7 +11189,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="302" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" ht="50.1" customHeight="1">
       <c r="A302" s="2" t="s">
         <v>9</v>
       </c>
@@ -11216,7 +11216,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="303" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" ht="50.1" customHeight="1">
       <c r="A303" s="2" t="s">
         <v>9</v>
       </c>
@@ -11243,7 +11243,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="304" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" ht="50.1" customHeight="1">
       <c r="A304" s="2" t="s">
         <v>9</v>
       </c>
@@ -11270,7 +11270,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="305" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" ht="50.1" customHeight="1">
       <c r="A305" s="2" t="s">
         <v>9</v>
       </c>
@@ -11297,7 +11297,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="306" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" ht="50.1" customHeight="1">
       <c r="A306" s="2" t="s">
         <v>9</v>
       </c>
@@ -11324,7 +11324,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="307" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" ht="50.1" customHeight="1">
       <c r="A307" s="2" t="s">
         <v>9</v>
       </c>
@@ -11351,7 +11351,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="308" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" ht="50.1" customHeight="1">
       <c r="A308" s="2" t="s">
         <v>9</v>
       </c>
@@ -11378,7 +11378,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="309" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" ht="50.1" customHeight="1">
       <c r="A309" s="2" t="s">
         <v>9</v>
       </c>
@@ -11405,7 +11405,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="310" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" ht="50.1" customHeight="1">
       <c r="A310" s="2" t="s">
         <v>9</v>
       </c>
@@ -11432,7 +11432,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="311" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" ht="50.1" customHeight="1">
       <c r="A311" s="2" t="s">
         <v>9</v>
       </c>
@@ -11459,7 +11459,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="312" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" ht="50.1" customHeight="1">
       <c r="A312" s="2" t="s">
         <v>9</v>
       </c>
@@ -11486,7 +11486,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="313" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" ht="50.1" customHeight="1">
       <c r="A313" s="2" t="s">
         <v>9</v>
       </c>
@@ -11513,7 +11513,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="314" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" ht="50.1" customHeight="1">
       <c r="A314" s="2" t="s">
         <v>9</v>
       </c>
@@ -11540,7 +11540,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="315" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" ht="50.1" customHeight="1">
       <c r="A315" s="2" t="s">
         <v>9</v>
       </c>
@@ -11567,7 +11567,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="316" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" ht="50.1" customHeight="1">
       <c r="A316" s="2" t="s">
         <v>9</v>
       </c>
@@ -11594,7 +11594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" ht="50.1" customHeight="1">
       <c r="A317" s="2" t="s">
         <v>9</v>
       </c>
@@ -11621,7 +11621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" ht="50.1" customHeight="1">
       <c r="A318" s="2" t="s">
         <v>9</v>
       </c>
@@ -11648,7 +11648,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="319" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" ht="50.1" customHeight="1">
       <c r="A319" s="2" t="s">
         <v>9</v>
       </c>
@@ -11675,7 +11675,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="320" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" ht="50.1" customHeight="1">
       <c r="A320" s="2" t="s">
         <v>9</v>
       </c>
@@ -11702,7 +11702,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="321" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" ht="50.1" customHeight="1">
       <c r="A321" s="2" t="s">
         <v>9</v>
       </c>
@@ -11729,7 +11729,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="322" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" ht="50.1" customHeight="1">
       <c r="A322" s="2" t="s">
         <v>9</v>
       </c>
@@ -11756,7 +11756,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="323" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" ht="50.1" customHeight="1">
       <c r="A323" s="2" t="s">
         <v>9</v>
       </c>
@@ -11783,7 +11783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" ht="50.1" customHeight="1">
       <c r="A324" s="2" t="s">
         <v>9</v>
       </c>
@@ -11810,7 +11810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" ht="50.1" customHeight="1">
       <c r="A325" s="2" t="s">
         <v>9</v>
       </c>
@@ -11838,11 +11838,232 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="tgujGZGwb8ZRvZRp8MciFCkBTXNs1qz0KEHVRCCyMd+TZz9pTo45D0M/0ibcejrIFmZlNor1fyvR+2lWCx27nA==" saltValue="D5UjxA81fy3EMdG+QKD44w==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection sort="0" autoFilter="0"/>
   <protectedRanges>
     <protectedRange algorithmName="SHA-512" hashValue="Aj2BVNLUwN0VdbcnC7KIvpLCSQSLfjguuZKP3fIkSLI2DpPPGKU3yv+wOvZw9eiBqQU8BBqiNRVeiv+51kESQg==" saltValue="HEFcR/nbhXx4rfjBlLagaA==" spinCount="100000" sqref="A1:I325" name="AllowSortFilter"/>
   </protectedRanges>
   <autoFilter ref="A1:I325" xr:uid="{D44A3233-1477-4964-AC3F-567ED4F9E6FB}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A1C7DD37AE641E4B9B3FD2F75B2D99BC" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6b9cb41f595aff4764e09aef2b23c1ed">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ea7a09a4-fe73-437e-8a86-996460e9b058" xmlns:ns3="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="daad8a4a6daff5298e6b89d91afce8e3" ns2:_="" ns3:_="">
+    <xsd:import namespace="ea7a09a4-fe73-437e-8a86-996460e9b058"/>
+    <xsd:import namespace="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ea7a09a4-fe73-437e-8a86-996460e9b058" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="d2f5926c-fefe-46c4-85d9-9ef0eea46f5c" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{6fbb2a74-2168-4404-a595-59f9a11d4eed}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea7a09a4-fe73-437e-8a86-996460e9b058">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5500D19-4A55-4093-88A8-F2A3B55AA618}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D60B303A-1A65-4176-91F9-48429F21A301}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FB9D389-0DA8-4145-9956-093B22175D7C}"/>
 </file>